--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA71DCC-757A-47A8-8E2A-BB6EBDE01449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43FEFF0C-FE85-4E00-A290-BDF63BF656BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
     <t>Abdulkadir Mohamed</t>
   </si>
   <si>
-    <t>04/04/1975</t>
+    <t>04/04/1975 00:00:00</t>
   </si>
   <si>
     <t>Tanzannie</t>
@@ -67,10 +67,10 @@
     <t>M</t>
   </si>
   <si>
-    <t>17/09/2024</t>
-  </si>
-  <si>
-    <t>01/01/1900</t>
+    <t>17/09/2024 00:00:00</t>
+  </si>
+  <si>
+    <t>01/01/1900 00:00:00</t>
   </si>
   <si>
     <t>BATOL</t>
@@ -79,7 +79,7 @@
     <t>Hassan</t>
   </si>
   <si>
-    <t>15/05/1997</t>
+    <t>15/05/1997 00:00:00</t>
   </si>
   <si>
     <t>Soudan</t>
@@ -88,7 +88,7 @@
     <t>F</t>
   </si>
   <si>
-    <t>01/09/2024</t>
+    <t>01/09/2024 00:00:00</t>
   </si>
   <si>
     <t>BEZHANISHVILI</t>
@@ -97,13 +97,13 @@
     <t>Zurab</t>
   </si>
   <si>
-    <t>30/06/1974</t>
+    <t>30/06/1974 00:00:00</t>
   </si>
   <si>
     <t>Géorgie</t>
   </si>
   <si>
-    <t>06/02/2025</t>
+    <t>06/02/2025 00:00:00</t>
   </si>
   <si>
     <t>BOUZID</t>
@@ -112,13 +112,13 @@
     <t>Bouchra</t>
   </si>
   <si>
-    <t>01/01/1983</t>
+    <t>01/01/1983 00:00:00</t>
   </si>
   <si>
     <t>Maroc</t>
   </si>
   <si>
-    <t>24/03/2023</t>
+    <t>24/03/2023 00:00:00</t>
   </si>
   <si>
     <t>KALANDIA</t>
@@ -127,10 +127,10 @@
     <t>Tamar</t>
   </si>
   <si>
-    <t>09/10/1979</t>
-  </si>
-  <si>
-    <t>22/05/2024</t>
+    <t>09/10/1979 00:00:00</t>
+  </si>
+  <si>
+    <t>22/05/2024 00:00:00</t>
   </si>
   <si>
     <t>KHACHATRYAN</t>
@@ -139,13 +139,13 @@
     <t>Rita</t>
   </si>
   <si>
-    <t>21/01/1973</t>
+    <t>21/01/1973 00:00:00</t>
   </si>
   <si>
     <t>Arménie</t>
   </si>
   <si>
-    <t>01/10/2024</t>
+    <t>01/10/2024 00:00:00</t>
   </si>
   <si>
     <t>KHUTSISHVILI</t>
@@ -154,7 +154,7 @@
     <t>Rusudan</t>
   </si>
   <si>
-    <t>08/11/1987</t>
+    <t>08/11/1987 00:00:00</t>
   </si>
   <si>
     <t>LENGO</t>
@@ -163,13 +163,13 @@
     <t>Lucoqui</t>
   </si>
   <si>
-    <t>07/11/1984</t>
+    <t>07/11/1984 00:00:00</t>
   </si>
   <si>
     <t>Angola</t>
   </si>
   <si>
-    <t>24/04/2025</t>
+    <t>24/04/2025 00:00:00</t>
   </si>
   <si>
     <t>MAMBA</t>
@@ -178,10 +178,10 @@
     <t>Benayi</t>
   </si>
   <si>
-    <t>15/07/1985</t>
-  </si>
-  <si>
-    <t>12/09/2024</t>
+    <t>15/07/1985 00:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2024 00:00:00</t>
   </si>
   <si>
     <t>MANTUIKA</t>
@@ -190,10 +190,10 @@
     <t>Sara</t>
   </si>
   <si>
-    <t>15/12/1999</t>
-  </si>
-  <si>
-    <t>23/09/2025</t>
+    <t>15/12/1999 00:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2025 00:00:00</t>
   </si>
   <si>
     <t>MEHMOOD</t>
@@ -202,13 +202,13 @@
     <t>Aamir</t>
   </si>
   <si>
-    <t>15/05/1990</t>
+    <t>15/05/1990 00:00:00</t>
   </si>
   <si>
     <t>Pakistan</t>
   </si>
   <si>
-    <t>12/01/2025</t>
+    <t>12/01/2025 00:00:00</t>
   </si>
   <si>
     <t>MIAH</t>
@@ -217,13 +217,13 @@
     <t>Mowab</t>
   </si>
   <si>
-    <t>28/05/1995</t>
+    <t>28/05/1995 00:00:00</t>
   </si>
   <si>
     <t>Bangladesh</t>
   </si>
   <si>
-    <t>01/09/2023</t>
+    <t>01/09/2023 00:00:00</t>
   </si>
   <si>
     <t>MOHAMED EL NOUR</t>
@@ -232,10 +232,10 @@
     <t>Abdel</t>
   </si>
   <si>
-    <t>19/01/1977</t>
-  </si>
-  <si>
-    <t>01/09/2025</t>
+    <t>19/01/1977 00:00:00</t>
+  </si>
+  <si>
+    <t>01/09/2025 00:00:00</t>
   </si>
   <si>
     <t>MOHD</t>
@@ -244,13 +244,13 @@
     <t>Azeem Pacha</t>
   </si>
   <si>
-    <t>04/04/1991</t>
+    <t>04/04/1991 00:00:00</t>
   </si>
   <si>
     <t>Inde</t>
   </si>
   <si>
-    <t>21/01/2025</t>
+    <t>21/01/2025 00:00:00</t>
   </si>
   <si>
     <t>NDUGBE</t>
@@ -259,13 +259,13 @@
     <t>Josiah</t>
   </si>
   <si>
-    <t>10/10/1982</t>
+    <t>10/10/1982 00:00:00</t>
   </si>
   <si>
     <t>Nigéria</t>
   </si>
   <si>
-    <t>19/11/2023</t>
+    <t>19/11/2023 00:00:00</t>
   </si>
   <si>
     <t>NEHREBA</t>
@@ -274,13 +274,13 @@
     <t>Iryna</t>
   </si>
   <si>
-    <t>28/02/1987</t>
+    <t>28/02/1987 00:00:00</t>
   </si>
   <si>
     <t>Ukraine</t>
   </si>
   <si>
-    <t>21/11/2024</t>
+    <t>21/11/2024 00:00:00</t>
   </si>
   <si>
     <t>OMAR</t>
@@ -289,7 +289,7 @@
     <t>Mohammed</t>
   </si>
   <si>
-    <t>01/01/1994</t>
+    <t>01/01/1994 00:00:00</t>
   </si>
   <si>
     <t>OVERCHENKO</t>
@@ -298,10 +298,10 @@
     <t>Aleksandrova</t>
   </si>
   <si>
-    <t>30/09/1971</t>
-  </si>
-  <si>
-    <t>10/09/2024</t>
+    <t>30/09/1971 00:00:00</t>
+  </si>
+  <si>
+    <t>10/09/2024 00:00:00</t>
   </si>
   <si>
     <t>PINTO</t>
@@ -310,7 +310,7 @@
     <t>Janet</t>
   </si>
   <si>
-    <t>23/02/1971</t>
+    <t>23/02/1971 00:00:00</t>
   </si>
   <si>
     <t>Pérou</t>
@@ -322,7 +322,7 @@
     <t>Daleep</t>
   </si>
   <si>
-    <t>01/09/1984</t>
+    <t>01/09/1984 00:00:00</t>
   </si>
   <si>
     <t>Afghanistan</t>
@@ -334,7 +334,7 @@
     <t>Ahmed</t>
   </si>
   <si>
-    <t>01/01/1998</t>
+    <t>01/01/1998 00:00:00</t>
   </si>
   <si>
     <t>Somalie</t>
@@ -346,13 +346,13 @@
     <t>Malika</t>
   </si>
   <si>
-    <t>01/09/1956</t>
+    <t>01/09/1956 00:00:00</t>
   </si>
   <si>
     <t>Espagne</t>
   </si>
   <si>
-    <t>16/11/2023</t>
+    <t>16/11/2023 00:00:00</t>
   </si>
   <si>
     <t>YLDIRIM DOGAN</t>
@@ -361,7 +361,7 @@
     <t>Ozgun</t>
   </si>
   <si>
-    <t>01/07/1979</t>
+    <t>01/07/1979 00:00:00</t>
   </si>
   <si>
     <t>Turquie</t>
@@ -851,7 +851,7 @@
     <col min="5" max="5" width="11.85546875" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="9" customWidth="1"/>
     <col min="7" max="7" width="15.140625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">

--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43FEFF0C-FE85-4E00-A290-BDF63BF656BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7508879-A180-4BBA-82D8-79AF88B3FADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
     <t>Abdulkadir Mohamed</t>
   </si>
   <si>
-    <t>04/04/1975 00:00:00</t>
+    <t>04/04/1975</t>
   </si>
   <si>
     <t>Tanzannie</t>
@@ -67,10 +67,10 @@
     <t>M</t>
   </si>
   <si>
-    <t>17/09/2024 00:00:00</t>
-  </si>
-  <si>
-    <t>01/01/1900 00:00:00</t>
+    <t>17/09/2024</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
   </si>
   <si>
     <t>BATOL</t>
@@ -79,7 +79,7 @@
     <t>Hassan</t>
   </si>
   <si>
-    <t>15/05/1997 00:00:00</t>
+    <t>15/05/1997</t>
   </si>
   <si>
     <t>Soudan</t>
@@ -88,7 +88,7 @@
     <t>F</t>
   </si>
   <si>
-    <t>01/09/2024 00:00:00</t>
+    <t>01/09/2024</t>
   </si>
   <si>
     <t>BEZHANISHVILI</t>
@@ -97,13 +97,13 @@
     <t>Zurab</t>
   </si>
   <si>
-    <t>30/06/1974 00:00:00</t>
+    <t>30/06/1974</t>
   </si>
   <si>
     <t>Géorgie</t>
   </si>
   <si>
-    <t>06/02/2025 00:00:00</t>
+    <t>06/02/2025</t>
   </si>
   <si>
     <t>BOUZID</t>
@@ -112,13 +112,13 @@
     <t>Bouchra</t>
   </si>
   <si>
-    <t>01/01/1983 00:00:00</t>
+    <t>01/01/1983</t>
   </si>
   <si>
     <t>Maroc</t>
   </si>
   <si>
-    <t>24/03/2023 00:00:00</t>
+    <t>24/03/2023</t>
   </si>
   <si>
     <t>KALANDIA</t>
@@ -127,10 +127,10 @@
     <t>Tamar</t>
   </si>
   <si>
-    <t>09/10/1979 00:00:00</t>
-  </si>
-  <si>
-    <t>22/05/2024 00:00:00</t>
+    <t>09/10/1979</t>
+  </si>
+  <si>
+    <t>22/05/2024</t>
   </si>
   <si>
     <t>KHACHATRYAN</t>
@@ -139,13 +139,13 @@
     <t>Rita</t>
   </si>
   <si>
-    <t>21/01/1973 00:00:00</t>
+    <t>21/01/1973</t>
   </si>
   <si>
     <t>Arménie</t>
   </si>
   <si>
-    <t>01/10/2024 00:00:00</t>
+    <t>01/10/2024</t>
   </si>
   <si>
     <t>KHUTSISHVILI</t>
@@ -154,7 +154,7 @@
     <t>Rusudan</t>
   </si>
   <si>
-    <t>08/11/1987 00:00:00</t>
+    <t>08/11/1987</t>
   </si>
   <si>
     <t>LENGO</t>
@@ -163,13 +163,13 @@
     <t>Lucoqui</t>
   </si>
   <si>
-    <t>07/11/1984 00:00:00</t>
+    <t>07/11/1984</t>
   </si>
   <si>
     <t>Angola</t>
   </si>
   <si>
-    <t>24/04/2025 00:00:00</t>
+    <t>24/04/2025</t>
   </si>
   <si>
     <t>MAMBA</t>
@@ -178,10 +178,10 @@
     <t>Benayi</t>
   </si>
   <si>
-    <t>15/07/1985 00:00:00</t>
-  </si>
-  <si>
-    <t>12/09/2024 00:00:00</t>
+    <t>15/07/1985</t>
+  </si>
+  <si>
+    <t>12/09/2024</t>
   </si>
   <si>
     <t>MANTUIKA</t>
@@ -190,10 +190,10 @@
     <t>Sara</t>
   </si>
   <si>
-    <t>15/12/1999 00:00:00</t>
-  </si>
-  <si>
-    <t>23/09/2025 00:00:00</t>
+    <t>15/12/1999</t>
+  </si>
+  <si>
+    <t>23/09/2025</t>
   </si>
   <si>
     <t>MEHMOOD</t>
@@ -202,13 +202,13 @@
     <t>Aamir</t>
   </si>
   <si>
-    <t>15/05/1990 00:00:00</t>
+    <t>15/05/1990</t>
   </si>
   <si>
     <t>Pakistan</t>
   </si>
   <si>
-    <t>12/01/2025 00:00:00</t>
+    <t>12/01/2025</t>
   </si>
   <si>
     <t>MIAH</t>
@@ -217,13 +217,13 @@
     <t>Mowab</t>
   </si>
   <si>
-    <t>28/05/1995 00:00:00</t>
+    <t>28/05/1995</t>
   </si>
   <si>
     <t>Bangladesh</t>
   </si>
   <si>
-    <t>01/09/2023 00:00:00</t>
+    <t>01/09/2023</t>
   </si>
   <si>
     <t>MOHAMED EL NOUR</t>
@@ -232,10 +232,10 @@
     <t>Abdel</t>
   </si>
   <si>
-    <t>19/01/1977 00:00:00</t>
-  </si>
-  <si>
-    <t>01/09/2025 00:00:00</t>
+    <t>19/01/1977</t>
+  </si>
+  <si>
+    <t>01/09/2025</t>
   </si>
   <si>
     <t>MOHD</t>
@@ -244,13 +244,13 @@
     <t>Azeem Pacha</t>
   </si>
   <si>
-    <t>04/04/1991 00:00:00</t>
+    <t>04/04/1991</t>
   </si>
   <si>
     <t>Inde</t>
   </si>
   <si>
-    <t>21/01/2025 00:00:00</t>
+    <t>21/01/2025</t>
   </si>
   <si>
     <t>NDUGBE</t>
@@ -259,13 +259,13 @@
     <t>Josiah</t>
   </si>
   <si>
-    <t>10/10/1982 00:00:00</t>
+    <t>10/10/1982</t>
   </si>
   <si>
     <t>Nigéria</t>
   </si>
   <si>
-    <t>19/11/2023 00:00:00</t>
+    <t>19/11/2023</t>
   </si>
   <si>
     <t>NEHREBA</t>
@@ -274,13 +274,13 @@
     <t>Iryna</t>
   </si>
   <si>
-    <t>28/02/1987 00:00:00</t>
+    <t>28/02/1987</t>
   </si>
   <si>
     <t>Ukraine</t>
   </si>
   <si>
-    <t>21/11/2024 00:00:00</t>
+    <t>21/11/2024</t>
   </si>
   <si>
     <t>OMAR</t>
@@ -289,7 +289,7 @@
     <t>Mohammed</t>
   </si>
   <si>
-    <t>01/01/1994 00:00:00</t>
+    <t>01/01/1994</t>
   </si>
   <si>
     <t>OVERCHENKO</t>
@@ -298,10 +298,10 @@
     <t>Aleksandrova</t>
   </si>
   <si>
-    <t>30/09/1971 00:00:00</t>
-  </si>
-  <si>
-    <t>10/09/2024 00:00:00</t>
+    <t>30/09/1971</t>
+  </si>
+  <si>
+    <t>10/09/2024</t>
   </si>
   <si>
     <t>PINTO</t>
@@ -310,7 +310,7 @@
     <t>Janet</t>
   </si>
   <si>
-    <t>23/02/1971 00:00:00</t>
+    <t>23/02/1971</t>
   </si>
   <si>
     <t>Pérou</t>
@@ -322,7 +322,7 @@
     <t>Daleep</t>
   </si>
   <si>
-    <t>01/09/1984 00:00:00</t>
+    <t>01/09/1984</t>
   </si>
   <si>
     <t>Afghanistan</t>
@@ -334,7 +334,7 @@
     <t>Ahmed</t>
   </si>
   <si>
-    <t>01/01/1998 00:00:00</t>
+    <t>01/01/1998</t>
   </si>
   <si>
     <t>Somalie</t>
@@ -346,13 +346,13 @@
     <t>Malika</t>
   </si>
   <si>
-    <t>01/09/1956 00:00:00</t>
+    <t>01/09/1956</t>
   </si>
   <si>
     <t>Espagne</t>
   </si>
   <si>
-    <t>16/11/2023 00:00:00</t>
+    <t>16/11/2023</t>
   </si>
   <si>
     <t>YLDIRIM DOGAN</t>
@@ -361,7 +361,7 @@
     <t>Ozgun</t>
   </si>
   <si>
-    <t>01/07/1979 00:00:00</t>
+    <t>01/07/1979</t>
   </si>
   <si>
     <t>Turquie</t>
@@ -851,7 +851,7 @@
     <col min="5" max="5" width="11.85546875" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="9" customWidth="1"/>
     <col min="7" max="7" width="15.140625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">

--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7508879-A180-4BBA-82D8-79AF88B3FADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642D0E60-AAC7-4649-8425-32E664E3A5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642D0E60-AAC7-4649-8425-32E664E3A5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5273E2D6-9E7B-48DD-8674-A8182B525455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5273E2D6-9E7B-48DD-8674-A8182B525455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2987475-FBB4-48FC-86D3-1AC3DBBDD5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2987475-FBB4-48FC-86D3-1AC3DBBDD5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B94AE0-88E0-4DA4-9E84-54EE36E1EDD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
